--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.5904602839019</v>
+        <v>7.083449796134059</v>
       </c>
       <c r="D2" t="n">
-        <v>67.38901428620193</v>
+        <v>10.95071482150781</v>
       </c>
       <c r="E2" t="n">
-        <v>14.91697665255618</v>
+        <v>2.424008706040379</v>
       </c>
       <c r="F2" t="n">
-        <v>6.826903734463515</v>
+        <v>1.109371856850321</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.57104025448833</v>
+        <v>8.867794041354355</v>
       </c>
       <c r="D3" t="n">
-        <v>55.42467991653785</v>
+        <v>9.006510486437401</v>
       </c>
       <c r="E3" t="n">
-        <v>14.91697665255618</v>
+        <v>2.424008706040379</v>
       </c>
       <c r="F3" t="n">
-        <v>6.826903734463515</v>
+        <v>1.109371856850321</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.90699932428372</v>
+        <v>7.947387390196106</v>
       </c>
       <c r="D4" t="n">
-        <v>49.85302718192138</v>
+        <v>8.101116917062225</v>
       </c>
       <c r="E4" t="n">
-        <v>14.91697665255618</v>
+        <v>2.424008706040379</v>
       </c>
       <c r="F4" t="n">
-        <v>6.826903734463515</v>
+        <v>1.109371856850321</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.73226679277372</v>
+        <v>4.993993353825729</v>
       </c>
       <c r="D5" t="n">
-        <v>55.38077228771328</v>
+        <v>8.999375496753409</v>
       </c>
       <c r="E5" t="n">
-        <v>14.91697665255618</v>
+        <v>2.424008706040379</v>
       </c>
       <c r="F5" t="n">
-        <v>6.826903734463515</v>
+        <v>1.109371856850321</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.52793842362506</v>
+        <v>9.185789993839073</v>
       </c>
       <c r="D6" t="n">
-        <v>56.35390113823139</v>
+        <v>9.157508934962602</v>
       </c>
       <c r="E6" t="n">
-        <v>14.91697665255618</v>
+        <v>2.424008706040379</v>
       </c>
       <c r="F6" t="n">
-        <v>6.826903734463515</v>
+        <v>1.109371856850321</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.31530305932181</v>
+        <v>4.113736747139794</v>
       </c>
       <c r="D7" t="n">
-        <v>49.63375050002414</v>
+        <v>8.065484456253921</v>
       </c>
       <c r="E7" t="n">
-        <v>14.91697665255618</v>
+        <v>2.424008706040379</v>
       </c>
       <c r="F7" t="n">
-        <v>6.826903734463515</v>
+        <v>1.109371856850321</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69897615918341</v>
+        <v>3.038583625867304</v>
       </c>
       <c r="D8" t="n">
-        <v>56.83756135735356</v>
+        <v>9.236103720569954</v>
       </c>
       <c r="E8" t="n">
-        <v>14.91697665255618</v>
+        <v>2.424008706040379</v>
       </c>
       <c r="F8" t="n">
-        <v>6.826903734463515</v>
+        <v>1.109371856850321</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>15.18138447467493</v>
+        <v>2.466974977134677</v>
       </c>
       <c r="D9" t="n">
-        <v>40.49407153106162</v>
+        <v>6.580286623797513</v>
       </c>
       <c r="E9" t="n">
-        <v>14.91697665255618</v>
+        <v>2.424008706040379</v>
       </c>
       <c r="F9" t="n">
-        <v>6.826903734463515</v>
+        <v>1.109371856850321</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.08148184604167</v>
+        <v>3.913240799981772</v>
       </c>
       <c r="D10" t="n">
-        <v>51.78802950489621</v>
+        <v>8.415554794545635</v>
       </c>
       <c r="E10" t="n">
-        <v>14.91697665255618</v>
+        <v>2.424008706040379</v>
       </c>
       <c r="F10" t="n">
-        <v>6.826903734463515</v>
+        <v>1.109371856850321</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
